--- a/Team-Data/2013-14/3-28-2013-14.xlsx
+++ b/Team-Data/2013-14/3-28-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,49 +806,49 @@
         <v>-1.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AF2" t="n">
         <v>18</v>
       </c>
       <c r="AG2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AI2" t="n">
         <v>18</v>
       </c>
       <c r="AJ2" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AM2" t="n">
         <v>2</v>
       </c>
       <c r="AN2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP2" t="n">
         <v>23</v>
       </c>
       <c r="AQ2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AR2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2" t="n">
         <v>20</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW2" t="n">
         <v>8</v>
@@ -802,7 +869,7 @@
         <v>25</v>
       </c>
       <c r="AY2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ2" t="n">
         <v>4</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E3" t="n">
         <v>23</v>
       </c>
       <c r="F3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G3" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
@@ -861,10 +928,10 @@
         <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>83.90000000000001</v>
+        <v>84</v>
       </c>
       <c r="K3" t="n">
-        <v>0.433</v>
+        <v>0.432</v>
       </c>
       <c r="L3" t="n">
         <v>6.7</v>
@@ -882,19 +949,19 @@
         <v>21</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.774</v>
+        <v>0.773</v>
       </c>
       <c r="R3" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="S3" t="n">
         <v>31</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V3" t="n">
         <v>15.2</v>
@@ -903,10 +970,10 @@
         <v>7.1</v>
       </c>
       <c r="X3" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>21.3</v>
@@ -915,13 +982,13 @@
         <v>19.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="AC3" t="n">
         <v>-4.1</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>26</v>
@@ -936,13 +1003,13 @@
         <v>27</v>
       </c>
       <c r="AI3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ3" t="n">
         <v>10</v>
       </c>
       <c r="AK3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL3" t="n">
         <v>23</v>
@@ -957,7 +1024,7 @@
         <v>24</v>
       </c>
       <c r="AP3" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ3" t="n">
         <v>10</v>
@@ -966,19 +1033,19 @@
         <v>7</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU3" t="n">
         <v>25</v>
       </c>
       <c r="AV3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW3" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F4" t="n">
         <v>33</v>
       </c>
       <c r="G4" t="n">
-        <v>0.535</v>
+        <v>0.529</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
       </c>
       <c r="I4" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J4" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K4" t="n">
-        <v>0.455</v>
+        <v>0.454</v>
       </c>
       <c r="L4" t="n">
         <v>8.5</v>
       </c>
       <c r="M4" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="N4" t="n">
-        <v>0.372</v>
+        <v>0.37</v>
       </c>
       <c r="O4" t="n">
         <v>18.8</v>
@@ -1076,10 +1143,10 @@
         <v>38.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V4" t="n">
-        <v>14.3</v>
+        <v>14.2</v>
       </c>
       <c r="W4" t="n">
         <v>8.5</v>
@@ -1088,22 +1155,22 @@
         <v>3.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Z4" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>98.5</v>
+        <v>98.3</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>14</v>
@@ -1124,16 +1191,16 @@
         <v>29</v>
       </c>
       <c r="AK4" t="n">
+        <v>13</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AM4" t="n">
         <v>11</v>
       </c>
-      <c r="AL4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>10</v>
-      </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AO4" t="n">
         <v>9</v>
@@ -1154,13 +1221,13 @@
         <v>29</v>
       </c>
       <c r="AU4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>28</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1207,34 +1274,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E5" t="n">
         <v>35</v>
       </c>
       <c r="F5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G5" t="n">
-        <v>0.479</v>
+        <v>0.486</v>
       </c>
       <c r="H5" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I5" t="n">
         <v>36.2</v>
       </c>
       <c r="J5" t="n">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="K5" t="n">
         <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M5" t="n">
-        <v>17.5</v>
+        <v>17.4</v>
       </c>
       <c r="N5" t="n">
         <v>0.352</v>
@@ -1243,7 +1310,7 @@
         <v>17.8</v>
       </c>
       <c r="P5" t="n">
-        <v>24.1</v>
+        <v>24.2</v>
       </c>
       <c r="Q5" t="n">
         <v>0.738</v>
@@ -1252,7 +1319,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="S5" t="n">
-        <v>32.8</v>
+        <v>32.9</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
@@ -1267,28 +1334,28 @@
         <v>6.1</v>
       </c>
       <c r="X5" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y5" t="n">
         <v>5.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>18.3</v>
+        <v>18.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.40000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="AC5" t="n">
         <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF5" t="n">
         <v>17</v>
@@ -1297,22 +1364,22 @@
         <v>17</v>
       </c>
       <c r="AH5" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AI5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>26</v>
       </c>
       <c r="AM5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AN5" t="n">
         <v>21</v>
@@ -1330,10 +1397,10 @@
         <v>25</v>
       </c>
       <c r="AS5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AT5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AU5" t="n">
         <v>18</v>
@@ -1345,7 +1412,7 @@
         <v>29</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY5" t="n">
         <v>20</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1389,55 +1456,55 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.6</v>
       </c>
       <c r="I6" t="n">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="J6" t="n">
-        <v>80.40000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="K6" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="L6" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M6" t="n">
         <v>17.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.344</v>
+        <v>0.347</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="Q6" t="n">
         <v>0.775</v>
       </c>
       <c r="R6" t="n">
-        <v>11.8</v>
+        <v>11.7</v>
       </c>
       <c r="S6" t="n">
         <v>33</v>
       </c>
       <c r="T6" t="n">
-        <v>44.8</v>
+        <v>44.7</v>
       </c>
       <c r="U6" t="n">
         <v>22.3</v>
@@ -1449,7 +1516,7 @@
         <v>7.2</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
         <v>6.2</v>
@@ -1458,25 +1525,25 @@
         <v>19.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.8</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AD6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE6" t="n">
         <v>12</v>
       </c>
-      <c r="AE6" t="n">
-        <v>13</v>
-      </c>
       <c r="AF6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>4</v>
@@ -1494,34 +1561,34 @@
         <v>27</v>
       </c>
       <c r="AM6" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AN6" t="n">
         <v>25</v>
       </c>
       <c r="AO6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>9</v>
       </c>
       <c r="AR6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT6" t="n">
         <v>9</v>
       </c>
       <c r="AU6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW6" t="n">
         <v>22</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1571,16 +1638,16 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E7" t="n">
         <v>29</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>0.392</v>
+        <v>0.397</v>
       </c>
       <c r="H7" t="n">
         <v>48.6</v>
@@ -1589,43 +1656,43 @@
         <v>36.6</v>
       </c>
       <c r="J7" t="n">
-        <v>84.59999999999999</v>
+        <v>84.5</v>
       </c>
       <c r="K7" t="n">
         <v>0.433</v>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M7" t="n">
         <v>20</v>
       </c>
       <c r="N7" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O7" t="n">
         <v>17</v>
       </c>
       <c r="P7" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.748</v>
+        <v>0.747</v>
       </c>
       <c r="R7" t="n">
         <v>12.2</v>
       </c>
       <c r="S7" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="T7" t="n">
-        <v>44.1</v>
+        <v>44.2</v>
       </c>
       <c r="U7" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="V7" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="W7" t="n">
         <v>7</v>
@@ -1646,7 +1713,7 @@
         <v>97.3</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.3</v>
+        <v>-4.2</v>
       </c>
       <c r="AD7" t="n">
         <v>1</v>
@@ -1667,10 +1734,10 @@
         <v>22</v>
       </c>
       <c r="AJ7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK7" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL7" t="n">
         <v>18</v>
@@ -1688,19 +1755,19 @@
         <v>18</v>
       </c>
       <c r="AQ7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AT7" t="n">
         <v>11</v>
       </c>
       <c r="AU7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV7" t="n">
         <v>11</v>
@@ -1721,7 +1788,7 @@
         <v>25</v>
       </c>
       <c r="BB7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC7" t="n">
         <v>25</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>2.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE8" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>11</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI8" t="n">
         <v>2</v>
@@ -1861,7 +1928,7 @@
         <v>13</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AO8" t="n">
         <v>16</v>
@@ -1882,10 +1949,10 @@
         <v>26</v>
       </c>
       <c r="AU8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AW8" t="n">
         <v>3</v>
@@ -1894,7 +1961,7 @@
         <v>23</v>
       </c>
       <c r="AY8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ8" t="n">
         <v>14</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
         <v>32</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" t="n">
-        <v>0.438</v>
+        <v>0.444</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J9" t="n">
         <v>85.40000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M9" t="n">
         <v>23.4</v>
       </c>
       <c r="N9" t="n">
-        <v>0.359</v>
+        <v>0.361</v>
       </c>
       <c r="O9" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="P9" t="n">
-        <v>26.5</v>
+        <v>26.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.72</v>
+        <v>0.719</v>
       </c>
       <c r="R9" t="n">
         <v>12.2</v>
@@ -1983,46 +2050,46 @@
         <v>33</v>
       </c>
       <c r="T9" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U9" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="V9" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="W9" t="n">
         <v>7.5</v>
       </c>
       <c r="X9" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y9" t="n">
         <v>5.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA9" t="n">
         <v>21.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>103.7</v>
+        <v>103.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>-2.6</v>
+        <v>-2.2</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
         <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>29</v>
@@ -2037,7 +2104,7 @@
         <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM9" t="n">
         <v>9</v>
@@ -2058,13 +2125,13 @@
         <v>4</v>
       </c>
       <c r="AS9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV9" t="n">
         <v>28</v>
@@ -2073,13 +2140,13 @@
         <v>18</v>
       </c>
       <c r="AX9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2088,7 +2155,7 @@
         <v>9</v>
       </c>
       <c r="BC9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -2117,55 +2184,55 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E10" t="n">
         <v>26</v>
       </c>
       <c r="F10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G10" t="n">
-        <v>0.361</v>
+        <v>0.366</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J10" t="n">
-        <v>86.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K10" t="n">
         <v>0.449</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="M10" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.317</v>
+        <v>0.32</v>
       </c>
       <c r="O10" t="n">
         <v>16.7</v>
       </c>
       <c r="P10" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.666</v>
+        <v>0.665</v>
       </c>
       <c r="R10" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="S10" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="T10" t="n">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="U10" t="n">
         <v>21.1</v>
@@ -2186,16 +2253,16 @@
         <v>20.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>100.6</v>
+        <v>100.9</v>
       </c>
       <c r="AC10" t="n">
-        <v>-3.2</v>
+        <v>-2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>23</v>
@@ -2210,7 +2277,7 @@
         <v>18</v>
       </c>
       <c r="AI10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AJ10" t="n">
         <v>4</v>
@@ -2243,31 +2310,31 @@
         <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AU10" t="n">
         <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>11</v>
       </c>
       <c r="AY10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB10" t="n">
         <v>16</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>17</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>23</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="n">
         <v>27</v>
       </c>
       <c r="G11" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2329,13 +2396,13 @@
         <v>24.3</v>
       </c>
       <c r="N11" t="n">
-        <v>0.375</v>
+        <v>0.374</v>
       </c>
       <c r="O11" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="P11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="Q11" t="n">
         <v>0.752</v>
@@ -2350,34 +2417,34 @@
         <v>45.3</v>
       </c>
       <c r="U11" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V11" t="n">
-        <v>15.3</v>
+        <v>15.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
         <v>4.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2392,7 +2459,7 @@
         <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ11" t="n">
         <v>7</v>
@@ -2410,7 +2477,7 @@
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
@@ -2419,7 +2486,7 @@
         <v>18</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2428,16 +2495,16 @@
         <v>2</v>
       </c>
       <c r="AU11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AW11" t="n">
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>5.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,10 +2638,10 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ12" t="n">
         <v>28</v>
@@ -2610,7 +2677,7 @@
         <v>7</v>
       </c>
       <c r="AU12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV12" t="n">
         <v>29</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -2663,43 +2730,43 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" t="n">
         <v>52</v>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G13" t="n">
-        <v>0.712</v>
+        <v>0.722</v>
       </c>
       <c r="H13" t="n">
         <v>48.3</v>
       </c>
       <c r="I13" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J13" t="n">
         <v>80.59999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L13" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M13" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.35</v>
+        <v>0.351</v>
       </c>
       <c r="O13" t="n">
         <v>18.4</v>
       </c>
       <c r="P13" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q13" t="n">
         <v>0.785</v>
@@ -2714,7 +2781,7 @@
         <v>45.2</v>
       </c>
       <c r="U13" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V13" t="n">
         <v>15.2</v>
@@ -2723,7 +2790,7 @@
         <v>6.9</v>
       </c>
       <c r="X13" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y13" t="n">
         <v>4.7</v>
@@ -2735,16 +2802,16 @@
         <v>22</v>
       </c>
       <c r="AB13" t="n">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF13" t="n">
         <v>3</v>
@@ -2756,13 +2823,13 @@
         <v>21</v>
       </c>
       <c r="AI13" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AJ13" t="n">
         <v>26</v>
       </c>
       <c r="AK13" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL13" t="n">
         <v>24</v>
@@ -2777,10 +2844,10 @@
         <v>11</v>
       </c>
       <c r="AP13" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AR13" t="n">
         <v>22</v>
@@ -2789,13 +2856,13 @@
         <v>1</v>
       </c>
       <c r="AT13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW13" t="n">
         <v>26</v>
@@ -2804,16 +2871,16 @@
         <v>4</v>
       </c>
       <c r="AY13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ13" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>13</v>
       </c>
       <c r="BA13" t="n">
         <v>6</v>
       </c>
       <c r="BB13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC13" t="n">
         <v>4</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -2923,7 +2990,7 @@
         <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE14" t="n">
         <v>4</v>
@@ -2935,10 +3002,10 @@
         <v>4</v>
       </c>
       <c r="AH14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AJ14" t="n">
         <v>21</v>
@@ -2953,10 +3020,10 @@
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>2</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
         <v>24</v>
       </c>
       <c r="F15" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G15" t="n">
-        <v>0.333</v>
+        <v>0.338</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>38.1</v>
+        <v>38</v>
       </c>
       <c r="J15" t="n">
-        <v>84.8</v>
+        <v>84.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L15" t="n">
         <v>9.4</v>
@@ -3057,55 +3124,55 @@
         <v>24.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O15" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="P15" t="n">
-        <v>22.5</v>
+        <v>22.6</v>
       </c>
       <c r="Q15" t="n">
         <v>0.75</v>
       </c>
       <c r="R15" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S15" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="T15" t="n">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="U15" t="n">
         <v>23.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="X15" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y15" t="n">
         <v>4.7</v>
       </c>
       <c r="Z15" t="n">
-        <v>20.2</v>
+        <v>20.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AB15" t="n">
         <v>102.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>-6.4</v>
+        <v>-6</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>25</v>
@@ -3120,25 +3187,25 @@
         <v>30</v>
       </c>
       <c r="AI15" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AJ15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM15" t="n">
         <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AP15" t="n">
         <v>19</v>
@@ -3150,7 +3217,7 @@
         <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT15" t="n">
         <v>23</v>
@@ -3159,22 +3226,22 @@
         <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AW15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BB15" t="n">
         <v>12</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3209,22 +3276,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E16" t="n">
         <v>43</v>
       </c>
       <c r="F16" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G16" t="n">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
       </c>
       <c r="I16" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J16" t="n">
         <v>81.59999999999999</v>
@@ -3239,31 +3306,31 @@
         <v>13.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="P16" t="n">
         <v>20.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.746</v>
+        <v>0.748</v>
       </c>
       <c r="R16" t="n">
         <v>11.4</v>
       </c>
       <c r="S16" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T16" t="n">
-        <v>42.3</v>
+        <v>42.5</v>
       </c>
       <c r="U16" t="n">
         <v>21.6</v>
       </c>
       <c r="V16" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="W16" t="n">
         <v>7.6</v>
@@ -3272,31 +3339,31 @@
         <v>4.7</v>
       </c>
       <c r="Y16" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AB16" t="n">
         <v>95.59999999999999</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AF16" t="n">
         <v>9</v>
       </c>
       <c r="AG16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH16" t="n">
         <v>18</v>
@@ -3317,7 +3384,7 @@
         <v>30</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AO16" t="n">
         <v>30</v>
@@ -3326,22 +3393,22 @@
         <v>28</v>
       </c>
       <c r="AQ16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AU16" t="n">
         <v>15</v>
       </c>
       <c r="AV16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW16" t="n">
         <v>15</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F17" t="n">
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>38.7</v>
       </c>
       <c r="J17" t="n">
         <v>76.8</v>
       </c>
       <c r="K17" t="n">
-        <v>0.505</v>
+        <v>0.504</v>
       </c>
       <c r="L17" t="n">
         <v>8</v>
@@ -3421,7 +3488,7 @@
         <v>21.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.368</v>
+        <v>0.367</v>
       </c>
       <c r="O17" t="n">
         <v>17.7</v>
@@ -3436,16 +3503,16 @@
         <v>7.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.3</v>
+        <v>29.2</v>
       </c>
       <c r="T17" t="n">
-        <v>36.8</v>
+        <v>36.7</v>
       </c>
       <c r="U17" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V17" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W17" t="n">
         <v>9</v>
@@ -3457,28 +3524,28 @@
         <v>3</v>
       </c>
       <c r="Z17" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.2</v>
+        <v>103.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF17" t="n">
         <v>4</v>
       </c>
       <c r="AG17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH17" t="n">
         <v>11</v>
@@ -3499,13 +3566,13 @@
         <v>16</v>
       </c>
       <c r="AN17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO17" t="n">
         <v>15</v>
       </c>
       <c r="AP17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
         <v>15</v>
@@ -3538,7 +3605,7 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB17" t="n">
         <v>11</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.1</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3669,7 +3736,7 @@
         <v>27</v>
       </c>
       <c r="AJ18" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK18" t="n">
         <v>26</v>
@@ -3687,7 +3754,7 @@
         <v>23</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
         <v>19</v>
@@ -3699,7 +3766,7 @@
         <v>29</v>
       </c>
       <c r="AT18" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AU18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3755,61 +3822,61 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E19" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F19" t="n">
         <v>35</v>
       </c>
       <c r="G19" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H19" t="n">
         <v>48.2</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>38.6</v>
       </c>
       <c r="J19" t="n">
-        <v>87.5</v>
+        <v>87.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.443</v>
+        <v>0.44</v>
       </c>
       <c r="L19" t="n">
         <v>7.5</v>
       </c>
       <c r="M19" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O19" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="P19" t="n">
-        <v>27.9</v>
+        <v>27.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R19" t="n">
         <v>12.6</v>
       </c>
       <c r="S19" t="n">
-        <v>32.4</v>
+        <v>32.3</v>
       </c>
       <c r="T19" t="n">
         <v>44.9</v>
       </c>
       <c r="U19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="V19" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="W19" t="n">
         <v>8.699999999999999</v>
@@ -3821,19 +3888,19 @@
         <v>5.6</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB19" t="n">
-        <v>106.9</v>
+        <v>106.3</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3848,13 +3915,13 @@
         <v>23</v>
       </c>
       <c r="AI19" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ19" t="n">
         <v>2</v>
       </c>
       <c r="AK19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL19" t="n">
         <v>17</v>
@@ -3884,10 +3951,10 @@
         <v>8</v>
       </c>
       <c r="AU19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AV19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AW19" t="n">
         <v>4</v>
@@ -3896,7 +3963,7 @@
         <v>30</v>
       </c>
       <c r="AY19" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AZ19" t="n">
         <v>3</v>
@@ -3905,10 +3972,10 @@
         <v>2</v>
       </c>
       <c r="BB19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F20" t="n">
         <v>40</v>
       </c>
       <c r="G20" t="n">
-        <v>0.444</v>
+        <v>0.437</v>
       </c>
       <c r="H20" t="n">
         <v>48.5</v>
@@ -3955,7 +4022,7 @@
         <v>38.1</v>
       </c>
       <c r="J20" t="n">
-        <v>82.7</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K20" t="n">
         <v>0.46</v>
@@ -3967,13 +4034,13 @@
         <v>15.9</v>
       </c>
       <c r="N20" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O20" t="n">
         <v>18.1</v>
       </c>
       <c r="P20" t="n">
-        <v>23.5</v>
+        <v>23.4</v>
       </c>
       <c r="Q20" t="n">
         <v>0.771</v>
@@ -3982,19 +4049,19 @@
         <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>30.4</v>
+        <v>30.5</v>
       </c>
       <c r="T20" t="n">
         <v>42.2</v>
       </c>
       <c r="U20" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="V20" t="n">
         <v>13.9</v>
       </c>
       <c r="W20" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="X20" t="n">
         <v>6.4</v>
@@ -4006,34 +4073,34 @@
         <v>22.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AB20" t="n">
-        <v>100.2</v>
+        <v>100.1</v>
       </c>
       <c r="AC20" t="n">
-        <v>-2</v>
+        <v>-2.1</v>
       </c>
       <c r="AD20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF20" t="n">
         <v>18</v>
       </c>
       <c r="AG20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH20" t="n">
         <v>8</v>
       </c>
       <c r="AI20" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AK20" t="n">
         <v>9</v>
@@ -4048,10 +4115,10 @@
         <v>8</v>
       </c>
       <c r="AO20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP20" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AQ20" t="n">
         <v>11</v>
@@ -4063,10 +4130,10 @@
         <v>25</v>
       </c>
       <c r="AT20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
         <v>7</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -4119,16 +4186,16 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
         <v>30</v>
       </c>
       <c r="F21" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>0.411</v>
+        <v>0.417</v>
       </c>
       <c r="H21" t="n">
         <v>48.5</v>
@@ -4140,10 +4207,10 @@
         <v>82.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L21" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="M21" t="n">
         <v>24.6</v>
@@ -4152,19 +4219,19 @@
         <v>0.371</v>
       </c>
       <c r="O21" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="P21" t="n">
         <v>20.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.755</v>
+        <v>0.756</v>
       </c>
       <c r="R21" t="n">
         <v>10.8</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
         <v>40.7</v>
@@ -4179,10 +4246,10 @@
         <v>7.5</v>
       </c>
       <c r="X21" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="Z21" t="n">
         <v>22.1</v>
@@ -4191,13 +4258,13 @@
         <v>19.6</v>
       </c>
       <c r="AB21" t="n">
-        <v>98.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="AC21" t="n">
-        <v>-1.8</v>
+        <v>-1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE21" t="n">
         <v>21</v>
@@ -4209,13 +4276,13 @@
         <v>21</v>
       </c>
       <c r="AH21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AI21" t="n">
         <v>19</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AK21" t="n">
         <v>17</v>
@@ -4227,7 +4294,7 @@
         <v>5</v>
       </c>
       <c r="AN21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AO21" t="n">
         <v>29</v>
@@ -4263,13 +4330,13 @@
         <v>3</v>
       </c>
       <c r="AZ21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA21" t="n">
         <v>24</v>
       </c>
       <c r="BB21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC21" t="n">
         <v>19</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.736</v>
+        <v>0.732</v>
       </c>
       <c r="H22" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>39</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.8</v>
+        <v>83</v>
       </c>
       <c r="K22" t="n">
-        <v>0.472</v>
+        <v>0.471</v>
       </c>
       <c r="L22" t="n">
         <v>8.1</v>
@@ -4331,7 +4398,7 @@
         <v>22.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.364</v>
+        <v>0.363</v>
       </c>
       <c r="O22" t="n">
         <v>19.9</v>
@@ -4343,16 +4410,16 @@
         <v>0.803</v>
       </c>
       <c r="R22" t="n">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="S22" t="n">
         <v>34.3</v>
       </c>
       <c r="T22" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="U22" t="n">
-        <v>21.9</v>
+        <v>21.8</v>
       </c>
       <c r="V22" t="n">
         <v>15.8</v>
@@ -4373,13 +4440,13 @@
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>106</v>
+        <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE22" t="n">
         <v>2</v>
@@ -4391,13 +4458,13 @@
         <v>2</v>
       </c>
       <c r="AH22" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AK22" t="n">
         <v>6</v>
@@ -4421,13 +4488,13 @@
         <v>2</v>
       </c>
       <c r="AR22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AU22" t="n">
         <v>13</v>
@@ -4448,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="BA22" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -4483,19 +4550,19 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F23" t="n">
         <v>52</v>
       </c>
       <c r="G23" t="n">
-        <v>0.288</v>
+        <v>0.278</v>
       </c>
       <c r="H23" t="n">
-        <v>48.8</v>
+        <v>48.7</v>
       </c>
       <c r="I23" t="n">
         <v>36.9</v>
@@ -4516,31 +4583,31 @@
         <v>0.349</v>
       </c>
       <c r="O23" t="n">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="P23" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q23" t="n">
         <v>0.766</v>
       </c>
       <c r="R23" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S23" t="n">
-        <v>32.9</v>
+        <v>32.8</v>
       </c>
       <c r="T23" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U23" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V23" t="n">
         <v>14.6</v>
       </c>
       <c r="W23" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X23" t="n">
         <v>4.2</v>
@@ -4549,19 +4616,19 @@
         <v>5.6</v>
       </c>
       <c r="Z23" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AA23" t="n">
         <v>18.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>-5.1</v>
+        <v>-5.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE23" t="n">
         <v>28</v>
@@ -4576,13 +4643,13 @@
         <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ23" t="n">
         <v>13</v>
       </c>
       <c r="AK23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL23" t="n">
         <v>21</v>
@@ -4597,7 +4664,7 @@
         <v>26</v>
       </c>
       <c r="AP23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ23" t="n">
         <v>12</v>
@@ -4606,10 +4673,10 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
         <v>22</v>
@@ -4627,7 +4694,7 @@
         <v>25</v>
       </c>
       <c r="AZ23" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>30</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-11.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4755,7 +4822,7 @@
         <v>29</v>
       </c>
       <c r="AH24" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AI24" t="n">
         <v>17</v>
@@ -4776,10 +4843,10 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ24" t="n">
         <v>28</v>
@@ -4788,7 +4855,7 @@
         <v>8</v>
       </c>
       <c r="AS24" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AT24" t="n">
         <v>12</v>
@@ -4803,7 +4870,7 @@
         <v>1</v>
       </c>
       <c r="AX24" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY24" t="n">
         <v>30</v>
@@ -4815,7 +4882,7 @@
         <v>13</v>
       </c>
       <c r="BB24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F25" t="n">
         <v>29</v>
       </c>
       <c r="G25" t="n">
-        <v>0.603</v>
+        <v>0.597</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4865,19 +4932,19 @@
         <v>38.7</v>
       </c>
       <c r="J25" t="n">
-        <v>83.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L25" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M25" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0.377</v>
+        <v>0.376</v>
       </c>
       <c r="O25" t="n">
         <v>18.6</v>
@@ -4886,16 +4953,16 @@
         <v>24.6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.757</v>
+        <v>0.756</v>
       </c>
       <c r="R25" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="S25" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T25" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="U25" t="n">
         <v>19.3</v>
@@ -4907,40 +4974,40 @@
         <v>8.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
         <v>4</v>
       </c>
       <c r="Z25" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA25" t="n">
         <v>21.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>105.5</v>
+        <v>105.4</v>
       </c>
       <c r="AC25" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE25" t="n">
         <v>9</v>
       </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>25</v>
       </c>
       <c r="AI25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ25" t="n">
         <v>12</v>
@@ -4949,7 +5016,7 @@
         <v>7</v>
       </c>
       <c r="AL25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AM25" t="n">
         <v>4</v>
@@ -4967,13 +5034,13 @@
         <v>16</v>
       </c>
       <c r="AR25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AS25" t="n">
         <v>16</v>
       </c>
       <c r="AT25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AU25" t="n">
         <v>29</v>
@@ -4988,16 +5055,16 @@
         <v>17</v>
       </c>
       <c r="AY25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AZ25" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>11</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F26" t="n">
         <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>0.635</v>
+        <v>0.63</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,28 +5114,28 @@
         <v>39</v>
       </c>
       <c r="J26" t="n">
-        <v>87.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L26" t="n">
         <v>9.5</v>
       </c>
       <c r="M26" t="n">
-        <v>25.5</v>
+        <v>25.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.372</v>
+        <v>0.371</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="P26" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="R26" t="n">
         <v>12.6</v>
@@ -5080,31 +5147,31 @@
         <v>46.3</v>
       </c>
       <c r="U26" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="V26" t="n">
         <v>13.8</v>
       </c>
       <c r="W26" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="X26" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="Y26" t="n">
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>19.4</v>
+        <v>19.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>106.6</v>
+        <v>106.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AD26" t="n">
         <v>1</v>
@@ -5119,16 +5186,16 @@
         <v>7</v>
       </c>
       <c r="AH26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ26" t="n">
         <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL26" t="n">
         <v>1</v>
@@ -5137,13 +5204,13 @@
         <v>3</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AQ26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>1</v>
       </c>
       <c r="AU26" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV26" t="n">
         <v>6</v>
@@ -5179,7 +5246,7 @@
         <v>12</v>
       </c>
       <c r="BB26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC26" t="n">
         <v>8</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5211,49 +5278,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" t="n">
         <v>25</v>
       </c>
       <c r="F27" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.347</v>
+        <v>0.352</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>36.9</v>
+        <v>37</v>
       </c>
       <c r="J27" t="n">
         <v>82.5</v>
       </c>
       <c r="K27" t="n">
-        <v>0.447</v>
+        <v>0.448</v>
       </c>
       <c r="L27" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M27" t="n">
         <v>18.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O27" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="P27" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R27" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S27" t="n">
         <v>32.2</v>
@@ -5262,7 +5329,7 @@
         <v>44.3</v>
       </c>
       <c r="U27" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="V27" t="n">
         <v>15.4</v>
@@ -5274,7 +5341,7 @@
         <v>4</v>
       </c>
       <c r="Y27" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z27" t="n">
         <v>22.9</v>
@@ -5283,13 +5350,13 @@
         <v>23.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>101</v>
+        <v>101.3</v>
       </c>
       <c r="AC27" t="n">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
@@ -5301,16 +5368,16 @@
         <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ27" t="n">
         <v>19</v>
       </c>
       <c r="AK27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AL27" t="n">
         <v>25</v>
@@ -5322,7 +5389,7 @@
         <v>27</v>
       </c>
       <c r="AO27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP27" t="n">
         <v>4</v>
@@ -5331,7 +5398,7 @@
         <v>13</v>
       </c>
       <c r="AR27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AS27" t="n">
         <v>13</v>
@@ -5343,19 +5410,19 @@
         <v>30</v>
       </c>
       <c r="AV27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>23</v>
       </c>
       <c r="AZ27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA27" t="n">
         <v>3</v>
@@ -5364,7 +5431,7 @@
         <v>13</v>
       </c>
       <c r="BC27" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5393,43 +5460,43 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F28" t="n">
         <v>16</v>
       </c>
       <c r="G28" t="n">
-        <v>0.778</v>
+        <v>0.775</v>
       </c>
       <c r="H28" t="n">
         <v>48.2</v>
       </c>
       <c r="I28" t="n">
-        <v>40.7</v>
+        <v>40.5</v>
       </c>
       <c r="J28" t="n">
-        <v>83.09999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.49</v>
+        <v>0.488</v>
       </c>
       <c r="L28" t="n">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="M28" t="n">
         <v>21.2</v>
       </c>
       <c r="N28" t="n">
-        <v>0.401</v>
+        <v>0.398</v>
       </c>
       <c r="O28" t="n">
-        <v>15.8</v>
+        <v>15.9</v>
       </c>
       <c r="P28" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="Q28" t="n">
         <v>0.785</v>
@@ -5438,40 +5505,40 @@
         <v>9.1</v>
       </c>
       <c r="S28" t="n">
-        <v>34.2</v>
+        <v>34.1</v>
       </c>
       <c r="T28" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U28" t="n">
-        <v>25.5</v>
+        <v>25.3</v>
       </c>
       <c r="V28" t="n">
         <v>14.7</v>
       </c>
       <c r="W28" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AA28" t="n">
         <v>19.5</v>
       </c>
       <c r="AB28" t="n">
-        <v>105.7</v>
+        <v>105.4</v>
       </c>
       <c r="AC28" t="n">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
       <c r="AD28" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
@@ -5489,13 +5556,13 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AM28" t="n">
         <v>17</v>
@@ -5510,7 +5577,7 @@
         <v>29</v>
       </c>
       <c r="AQ28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR28" t="n">
         <v>27</v>
@@ -5540,10 +5607,10 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BC28" t="n">
         <v>1</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E29" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" t="n">
         <v>31</v>
       </c>
       <c r="G29" t="n">
-        <v>0.569</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H29" t="n">
         <v>48.8</v>
@@ -5599,31 +5666,31 @@
         <v>0.443</v>
       </c>
       <c r="L29" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M29" t="n">
         <v>23</v>
       </c>
       <c r="N29" t="n">
-        <v>0.367</v>
+        <v>0.369</v>
       </c>
       <c r="O29" t="n">
         <v>19.5</v>
       </c>
       <c r="P29" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.781</v>
+        <v>0.78</v>
       </c>
       <c r="R29" t="n">
-        <v>11.7</v>
+        <v>11.6</v>
       </c>
       <c r="S29" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="T29" t="n">
-        <v>43</v>
+        <v>43.1</v>
       </c>
       <c r="U29" t="n">
         <v>21.3</v>
@@ -5641,19 +5708,19 @@
         <v>4.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA29" t="n">
         <v>22</v>
       </c>
       <c r="AB29" t="n">
-        <v>101</v>
+        <v>100.9</v>
       </c>
       <c r="AC29" t="n">
         <v>3.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5677,13 +5744,13 @@
         <v>21</v>
       </c>
       <c r="AL29" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AM29" t="n">
         <v>10</v>
       </c>
       <c r="AN29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AO29" t="n">
         <v>6</v>
@@ -5692,22 +5759,22 @@
         <v>7</v>
       </c>
       <c r="AQ29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AR29" t="n">
         <v>12</v>
       </c>
       <c r="AS29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU29" t="n">
         <v>17</v>
       </c>
       <c r="AV29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW29" t="n">
         <v>23</v>
@@ -5716,7 +5783,7 @@
         <v>22</v>
       </c>
       <c r="AY29" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
@@ -5728,7 +5795,7 @@
         <v>15</v>
       </c>
       <c r="BC29" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5757,16 +5824,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E30" t="n">
         <v>23</v>
       </c>
       <c r="F30" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G30" t="n">
-        <v>0.315</v>
+        <v>0.319</v>
       </c>
       <c r="H30" t="n">
         <v>48.1</v>
@@ -5775,7 +5842,7 @@
         <v>35.7</v>
       </c>
       <c r="J30" t="n">
-        <v>80.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.442</v>
@@ -5787,34 +5854,34 @@
         <v>19.4</v>
       </c>
       <c r="N30" t="n">
-        <v>0.351</v>
+        <v>0.352</v>
       </c>
       <c r="O30" t="n">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="P30" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.746</v>
+        <v>0.745</v>
       </c>
       <c r="R30" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S30" t="n">
-        <v>30.2</v>
+        <v>30.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U30" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V30" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="W30" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X30" t="n">
         <v>4.5</v>
@@ -5823,10 +5890,10 @@
         <v>4.8</v>
       </c>
       <c r="Z30" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AB30" t="n">
         <v>94.40000000000001</v>
@@ -5835,7 +5902,7 @@
         <v>-6.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE30" t="n">
         <v>26</v>
@@ -5883,10 +5950,10 @@
         <v>26</v>
       </c>
       <c r="AT30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AU30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AV30" t="n">
         <v>13</v>
@@ -5898,13 +5965,13 @@
         <v>20</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ30" t="n">
         <v>17</v>
       </c>
       <c r="BA30" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BB30" t="n">
         <v>29</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
@@ -5939,46 +6006,46 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
         <v>35</v>
       </c>
       <c r="G31" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H31" t="n">
         <v>49</v>
       </c>
       <c r="I31" t="n">
-        <v>38.5</v>
+        <v>38.6</v>
       </c>
       <c r="J31" t="n">
         <v>84.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.454</v>
+        <v>0.455</v>
       </c>
       <c r="L31" t="n">
         <v>8.1</v>
       </c>
       <c r="M31" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="N31" t="n">
-        <v>0.385</v>
+        <v>0.386</v>
       </c>
       <c r="O31" t="n">
-        <v>15.6</v>
+        <v>15.5</v>
       </c>
       <c r="P31" t="n">
         <v>21.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.734</v>
+        <v>0.732</v>
       </c>
       <c r="R31" t="n">
         <v>11</v>
@@ -5993,7 +6060,7 @@
         <v>23.2</v>
       </c>
       <c r="V31" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W31" t="n">
         <v>8.300000000000001</v>
@@ -6002,7 +6069,7 @@
         <v>4.7</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Z31" t="n">
         <v>20.5</v>
@@ -6011,13 +6078,13 @@
         <v>19.7</v>
       </c>
       <c r="AB31" t="n">
-        <v>100.7</v>
+        <v>100.9</v>
       </c>
       <c r="AC31" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6032,13 +6099,13 @@
         <v>1</v>
       </c>
       <c r="AI31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ31" t="n">
         <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL31" t="n">
         <v>14</v>
@@ -6062,10 +6129,10 @@
         <v>16</v>
       </c>
       <c r="AS31" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU31" t="n">
         <v>7</v>
@@ -6080,7 +6147,7 @@
         <v>15</v>
       </c>
       <c r="AY31" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ31" t="n">
         <v>16</v>
@@ -6089,7 +6156,7 @@
         <v>23</v>
       </c>
       <c r="BB31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC31" t="n">
         <v>15</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-28-2013-14</t>
+          <t>2014-03-28</t>
         </is>
       </c>
     </row>
